--- a/psb-risk-module/ListOfTables_Paper9_revC_v1.xlsx
+++ b/psb-risk-module/ListOfTables_Paper9_revC_v1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3a07647642d852d6/forUBCOComp/H/UniformRiskMap/Results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OpenSees_PracticeExamples\ida-spo-msa\psb-risk-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8699D65-1DD6-4DC2-B66D-F4FE3E8AFD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="925"/>
   </bookViews>
   <sheets>
     <sheet name="TabFigList" sheetId="28" r:id="rId1"/>
@@ -66,7 +65,7 @@
     <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="9" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6632,7 +6631,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="11">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -10236,6 +10235,102 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10245,105 +10340,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10386,69 +10385,81 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -10456,29 +10467,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 5" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 6" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="3"/>
+    <cellStyle name="Normal 4" xfId="4"/>
+    <cellStyle name="Normal 5" xfId="6"/>
+    <cellStyle name="Normal 6" xfId="7"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
@@ -16542,7 +16541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet21">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
@@ -16555,7 +16554,7 @@
     <col min="4" max="4" width="9" style="13" customWidth="1"/>
     <col min="5" max="5" width="71.140625" style="13" customWidth="1"/>
     <col min="6" max="7" width="9.140625" style="13"/>
-    <col min="8" max="8" width="11.85546875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="13" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
@@ -16831,7 +16830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -17026,8 +17025,8 @@
       <c r="Q18" s="757" t="s">
         <v>443</v>
       </c>
-      <c r="R18" s="739"/>
-      <c r="S18" s="739"/>
+      <c r="R18" s="735"/>
+      <c r="S18" s="735"/>
       <c r="T18" s="758"/>
       <c r="U18" s="502" t="s">
         <v>437</v>
@@ -17035,8 +17034,8 @@
       <c r="V18" s="757" t="s">
         <v>444</v>
       </c>
-      <c r="W18" s="739"/>
-      <c r="X18" s="739"/>
+      <c r="W18" s="735"/>
+      <c r="X18" s="735"/>
       <c r="Y18" s="758"/>
       <c r="Z18" s="502" t="s">
         <v>438</v>
@@ -17044,8 +17043,8 @@
       <c r="AA18" s="757" t="s">
         <v>445</v>
       </c>
-      <c r="AB18" s="739"/>
-      <c r="AC18" s="739"/>
+      <c r="AB18" s="735"/>
+      <c r="AC18" s="735"/>
       <c r="AD18" s="758"/>
       <c r="AE18" s="502" t="s">
         <v>439</v>
@@ -17053,8 +17052,8 @@
       <c r="AF18" s="757" t="s">
         <v>446</v>
       </c>
-      <c r="AG18" s="739"/>
-      <c r="AH18" s="739"/>
+      <c r="AG18" s="735"/>
+      <c r="AH18" s="735"/>
       <c r="AI18" s="758"/>
       <c r="AJ18" s="502" t="s">
         <v>440</v>
@@ -17062,8 +17061,8 @@
       <c r="AK18" s="757" t="s">
         <v>447</v>
       </c>
-      <c r="AL18" s="739"/>
-      <c r="AM18" s="739"/>
+      <c r="AL18" s="735"/>
+      <c r="AM18" s="735"/>
       <c r="AN18" s="758"/>
     </row>
     <row r="19" spans="1:40" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19298,7 +19297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet22">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -19347,19 +19346,19 @@
       <c r="Z2"/>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="738" t="s">
+      <c r="A3" s="734" t="s">
         <v>637</v>
       </c>
-      <c r="B3" s="738"/>
-      <c r="C3" s="738"/>
-      <c r="D3" s="738"/>
-      <c r="E3" s="738"/>
-      <c r="F3" s="738"/>
-      <c r="G3" s="738"/>
-      <c r="H3" s="738"/>
-      <c r="I3" s="738"/>
-      <c r="J3" s="738"/>
-      <c r="K3" s="738"/>
+      <c r="B3" s="734"/>
+      <c r="C3" s="734"/>
+      <c r="D3" s="734"/>
+      <c r="E3" s="734"/>
+      <c r="F3" s="734"/>
+      <c r="G3" s="734"/>
+      <c r="H3" s="734"/>
+      <c r="I3" s="734"/>
+      <c r="J3" s="734"/>
+      <c r="K3" s="734"/>
       <c r="L3" s="544"/>
       <c r="M3" s="544"/>
       <c r="N3" s="544"/>
@@ -21307,19 +21306,19 @@
       </c>
     </row>
     <row r="33" spans="11:24" x14ac:dyDescent="0.25">
-      <c r="K33" s="738" t="s">
+      <c r="K33" s="734" t="s">
         <v>547</v>
       </c>
-      <c r="L33" s="738"/>
-      <c r="M33" s="738"/>
-      <c r="N33" s="738"/>
-      <c r="O33" s="738"/>
-      <c r="P33" s="738"/>
-      <c r="Q33" s="738"/>
-      <c r="R33" s="738"/>
-      <c r="S33" s="738"/>
-      <c r="T33" s="738"/>
-      <c r="U33" s="738"/>
+      <c r="L33" s="734"/>
+      <c r="M33" s="734"/>
+      <c r="N33" s="734"/>
+      <c r="O33" s="734"/>
+      <c r="P33" s="734"/>
+      <c r="Q33" s="734"/>
+      <c r="R33" s="734"/>
+      <c r="S33" s="734"/>
+      <c r="T33" s="734"/>
+      <c r="U33" s="734"/>
     </row>
     <row r="34" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K34" s="47" t="s">
@@ -21327,13 +21326,13 @@
       </c>
     </row>
     <row r="35" spans="11:24" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K35" s="738" t="s">
+      <c r="K35" s="734" t="s">
         <v>638</v>
       </c>
-      <c r="L35" s="738"/>
-      <c r="M35" s="738"/>
-      <c r="N35" s="738"/>
-      <c r="O35" s="738"/>
+      <c r="L35" s="734"/>
+      <c r="M35" s="734"/>
+      <c r="N35" s="734"/>
+      <c r="O35" s="734"/>
     </row>
     <row r="37" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K37" s="55" t="s">
@@ -21558,7 +21557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -23579,7 +23578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet23">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -23672,17 +23671,17 @@
       <c r="N3" s="13"/>
     </row>
     <row r="4" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="738" t="s">
+      <c r="A4" s="734" t="s">
         <v>639</v>
       </c>
-      <c r="B4" s="738"/>
-      <c r="C4" s="738"/>
-      <c r="D4" s="738"/>
-      <c r="E4" s="738"/>
-      <c r="F4" s="738"/>
-      <c r="G4" s="738"/>
-      <c r="H4" s="738"/>
-      <c r="I4" s="738"/>
+      <c r="B4" s="734"/>
+      <c r="C4" s="734"/>
+      <c r="D4" s="734"/>
+      <c r="E4" s="734"/>
+      <c r="F4" s="734"/>
+      <c r="G4" s="734"/>
+      <c r="H4" s="734"/>
+      <c r="I4" s="734"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="N4" s="13"/>
@@ -24799,7 +24798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet25">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -24832,15 +24831,15 @@
       <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="738" t="s">
+      <c r="A3" s="734" t="s">
         <v>640</v>
       </c>
-      <c r="B3" s="738"/>
-      <c r="C3" s="738"/>
-      <c r="D3" s="738"/>
-      <c r="E3" s="738"/>
-      <c r="F3" s="738"/>
-      <c r="G3" s="738"/>
+      <c r="B3" s="734"/>
+      <c r="C3" s="734"/>
+      <c r="D3" s="734"/>
+      <c r="E3" s="734"/>
+      <c r="F3" s="734"/>
+      <c r="G3" s="734"/>
       <c r="H3" s="13"/>
       <c r="I3" s="243" t="s">
         <v>205</v>
@@ -25337,7 +25336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet27">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -25367,15 +25366,15 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="738" t="s">
+      <c r="A3" s="734" t="s">
         <v>641</v>
       </c>
-      <c r="B3" s="738"/>
-      <c r="C3" s="738"/>
-      <c r="D3" s="738"/>
-      <c r="E3" s="738"/>
-      <c r="F3" s="738"/>
-      <c r="G3" s="738"/>
+      <c r="B3" s="734"/>
+      <c r="C3" s="734"/>
+      <c r="D3" s="734"/>
+      <c r="E3" s="734"/>
+      <c r="F3" s="734"/>
+      <c r="G3" s="734"/>
       <c r="H3" s="167"/>
       <c r="I3" s="167"/>
       <c r="J3" s="167"/>
@@ -25780,44 +25779,44 @@
       </c>
     </row>
     <row r="17" spans="1:41" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="739" t="s">
+      <c r="A17" s="735" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="752" t="s">
+      <c r="B17" s="748" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="752" t="s">
+      <c r="C17" s="748" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="768" t="s">
+      <c r="D17" s="784" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="770" t="s">
+      <c r="E17" s="782" t="s">
         <v>582</v>
       </c>
-      <c r="F17" s="771"/>
-      <c r="G17" s="772"/>
-      <c r="H17" s="770" t="s">
+      <c r="F17" s="783"/>
+      <c r="G17" s="786"/>
+      <c r="H17" s="782" t="s">
         <v>127</v>
       </c>
-      <c r="I17" s="771"/>
-      <c r="J17" s="772"/>
-      <c r="K17" s="770" t="s">
+      <c r="I17" s="783"/>
+      <c r="J17" s="786"/>
+      <c r="K17" s="782" t="s">
         <v>453</v>
       </c>
-      <c r="L17" s="771"/>
-      <c r="M17" s="771"/>
-      <c r="N17" s="773" t="s">
+      <c r="L17" s="783"/>
+      <c r="M17" s="783"/>
+      <c r="N17" s="779" t="s">
         <v>127</v>
       </c>
-      <c r="O17" s="774"/>
-      <c r="P17" s="775"/>
-      <c r="Q17" s="773" t="s">
+      <c r="O17" s="780"/>
+      <c r="P17" s="781"/>
+      <c r="Q17" s="779" t="s">
         <v>453</v>
       </c>
-      <c r="R17" s="774"/>
-      <c r="S17" s="774"/>
-      <c r="U17" s="768" t="s">
+      <c r="R17" s="780"/>
+      <c r="S17" s="780"/>
+      <c r="U17" s="784" t="s">
         <v>152</v>
       </c>
       <c r="W17" s="710">
@@ -25845,10 +25844,10 @@
       <c r="AO17"/>
     </row>
     <row r="18" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="783"/>
-      <c r="B18" s="776"/>
-      <c r="C18" s="776"/>
-      <c r="D18" s="769"/>
+      <c r="A18" s="775"/>
+      <c r="B18" s="768"/>
+      <c r="C18" s="768"/>
+      <c r="D18" s="785"/>
       <c r="E18" s="717" t="s">
         <v>650</v>
       </c>
@@ -25894,7 +25893,7 @@
       <c r="S18" s="578" t="s">
         <v>581</v>
       </c>
-      <c r="U18" s="769"/>
+      <c r="U18" s="785"/>
       <c r="W18" s="702" t="s">
         <v>648</v>
       </c>
@@ -26529,21 +26528,21 @@
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
-      <c r="E29" s="784" t="s">
+      <c r="E29" s="776" t="s">
         <v>485</v>
       </c>
-      <c r="F29" s="785"/>
-      <c r="G29" s="786"/>
-      <c r="H29" s="773" t="s">
+      <c r="F29" s="777"/>
+      <c r="G29" s="778"/>
+      <c r="H29" s="779" t="s">
         <v>578</v>
       </c>
-      <c r="I29" s="774"/>
-      <c r="J29" s="775"/>
-      <c r="K29" s="773" t="s">
+      <c r="I29" s="780"/>
+      <c r="J29" s="781"/>
+      <c r="K29" s="779" t="s">
         <v>140</v>
       </c>
-      <c r="L29" s="774"/>
-      <c r="M29" s="775"/>
+      <c r="L29" s="780"/>
+      <c r="M29" s="781"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30"/>
@@ -26731,14 +26730,14 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
-      <c r="H37" s="777" t="s">
+      <c r="H37" s="769" t="s">
         <v>587</v>
       </c>
-      <c r="I37" s="778"/>
-      <c r="K37" s="777" t="s">
+      <c r="I37" s="770"/>
+      <c r="K37" s="769" t="s">
         <v>210</v>
       </c>
-      <c r="L37" s="778"/>
+      <c r="L37" s="770"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38"/>
@@ -26748,10 +26747,10 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38" s="779"/>
-      <c r="I38" s="780"/>
-      <c r="K38" s="779"/>
-      <c r="L38" s="780"/>
+      <c r="H38" s="771"/>
+      <c r="I38" s="772"/>
+      <c r="K38" s="771"/>
+      <c r="L38" s="772"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39"/>
@@ -26761,10 +26760,10 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
-      <c r="H39" s="779"/>
-      <c r="I39" s="780"/>
-      <c r="K39" s="779"/>
-      <c r="L39" s="780"/>
+      <c r="H39" s="771"/>
+      <c r="I39" s="772"/>
+      <c r="K39" s="771"/>
+      <c r="L39" s="772"/>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
@@ -26774,10 +26773,10 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
-      <c r="H40" s="781"/>
-      <c r="I40" s="782"/>
-      <c r="K40" s="781"/>
-      <c r="L40" s="782"/>
+      <c r="H40" s="773"/>
+      <c r="I40" s="774"/>
+      <c r="K40" s="773"/>
+      <c r="L40" s="774"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
@@ -26848,6 +26847,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="N17:P17"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="H37:I40"/>
@@ -26858,12 +26863,6 @@
     <mergeCell ref="H29:J29"/>
     <mergeCell ref="K29:M29"/>
     <mergeCell ref="K17:M17"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="N17:P17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26872,7 +26871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet29">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -27007,99 +27006,99 @@
       <c r="C5" s="628"/>
       <c r="D5" s="628"/>
       <c r="E5" s="630"/>
-      <c r="F5" s="795" t="s">
+      <c r="F5" s="788" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="795"/>
-      <c r="H5" s="795"/>
+      <c r="G5" s="788"/>
+      <c r="H5" s="788"/>
       <c r="I5" s="631" t="s">
         <v>148</v>
       </c>
-      <c r="J5" s="788" t="s">
+      <c r="J5" s="789" t="s">
         <v>149</v>
       </c>
-      <c r="K5" s="788"/>
-      <c r="L5" s="788"/>
+      <c r="K5" s="789"/>
+      <c r="L5" s="789"/>
       <c r="O5" s="628"/>
       <c r="P5" s="628"/>
       <c r="Q5" s="628"/>
       <c r="R5" s="628"/>
-      <c r="T5" s="788" t="s">
+      <c r="T5" s="789" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="788"/>
-      <c r="V5" s="788"/>
+      <c r="U5" s="789"/>
+      <c r="V5" s="789"/>
       <c r="W5" s="631" t="s">
         <v>148</v>
       </c>
-      <c r="X5" s="788" t="s">
+      <c r="X5" s="789" t="s">
         <v>149</v>
       </c>
-      <c r="Y5" s="788"/>
-      <c r="Z5" s="788"/>
+      <c r="Y5" s="789"/>
+      <c r="Z5" s="789"/>
       <c r="AC5" s="628"/>
       <c r="AD5" s="628"/>
       <c r="AE5" s="628"/>
       <c r="AF5" s="628"/>
-      <c r="AH5" s="788" t="s">
+      <c r="AH5" s="789" t="s">
         <v>151</v>
       </c>
-      <c r="AI5" s="788"/>
-      <c r="AJ5" s="788"/>
+      <c r="AI5" s="789"/>
+      <c r="AJ5" s="789"/>
       <c r="AK5" s="631" t="s">
         <v>148</v>
       </c>
-      <c r="AL5" s="788" t="s">
+      <c r="AL5" s="789" t="s">
         <v>149</v>
       </c>
-      <c r="AM5" s="788"/>
-      <c r="AN5" s="788"/>
+      <c r="AM5" s="789"/>
+      <c r="AN5" s="789"/>
     </row>
     <row r="6" spans="1:40" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="632"/>
       <c r="E6" s="633"/>
-      <c r="F6" s="792" t="s">
+      <c r="F6" s="790" t="s">
         <v>612</v>
       </c>
-      <c r="G6" s="793"/>
-      <c r="H6" s="794"/>
+      <c r="G6" s="791"/>
+      <c r="H6" s="792"/>
       <c r="I6" s="634" t="s">
         <v>613</v>
       </c>
-      <c r="J6" s="793" t="s">
+      <c r="J6" s="791" t="s">
         <v>614</v>
       </c>
-      <c r="K6" s="793"/>
-      <c r="L6" s="794"/>
+      <c r="K6" s="791"/>
+      <c r="L6" s="792"/>
       <c r="N6" s="635"/>
       <c r="R6" s="632"/>
-      <c r="T6" s="792" t="s">
+      <c r="T6" s="790" t="s">
         <v>615</v>
       </c>
-      <c r="U6" s="793"/>
-      <c r="V6" s="794"/>
+      <c r="U6" s="791"/>
+      <c r="V6" s="792"/>
       <c r="W6" s="636" t="s">
         <v>613</v>
       </c>
-      <c r="X6" s="792" t="s">
+      <c r="X6" s="790" t="s">
         <v>616</v>
       </c>
-      <c r="Y6" s="793"/>
-      <c r="Z6" s="794"/>
+      <c r="Y6" s="791"/>
+      <c r="Z6" s="792"/>
       <c r="AF6" s="632"/>
-      <c r="AH6" s="789" t="s">
+      <c r="AH6" s="793" t="s">
         <v>617</v>
       </c>
-      <c r="AI6" s="790"/>
-      <c r="AJ6" s="791"/>
+      <c r="AI6" s="794"/>
+      <c r="AJ6" s="795"/>
       <c r="AK6" s="636" t="s">
         <v>613</v>
       </c>
-      <c r="AL6" s="789" t="s">
+      <c r="AL6" s="793" t="s">
         <v>618</v>
       </c>
-      <c r="AM6" s="790"/>
-      <c r="AN6" s="791"/>
+      <c r="AM6" s="794"/>
+      <c r="AN6" s="795"/>
     </row>
     <row r="7" spans="1:40" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="637" t="s">
@@ -28853,21 +28852,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AC3:AL3"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="AL5:AN5"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AL6:AN6"/>
+    <mergeCell ref="O3:X3"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="X5:Z5"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="X6:Z6"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="J6:L6"/>
-    <mergeCell ref="O3:X3"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="X5:Z5"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="X6:Z6"/>
-    <mergeCell ref="AC3:AL3"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="AL5:AN5"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AL6:AN6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -28875,7 +28874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -28895,12 +28894,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="721" t="s">
+      <c r="A3" s="718" t="s">
         <v>645</v>
       </c>
-      <c r="B3" s="721"/>
-      <c r="C3" s="721"/>
-      <c r="D3" s="721"/>
+      <c r="B3" s="718"/>
+      <c r="C3" s="718"/>
+      <c r="D3" s="718"/>
       <c r="E3" s="262"/>
       <c r="F3" s="262"/>
       <c r="G3" s="262"/>
@@ -29004,7 +29003,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -29045,15 +29044,15 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="721" t="s">
+      <c r="A3" s="718" t="s">
         <v>634</v>
       </c>
-      <c r="B3" s="721"/>
-      <c r="C3" s="721"/>
-      <c r="D3" s="721"/>
-      <c r="E3" s="721"/>
-      <c r="F3" s="721"/>
-      <c r="G3" s="721"/>
+      <c r="B3" s="718"/>
+      <c r="C3" s="718"/>
+      <c r="D3" s="718"/>
+      <c r="E3" s="718"/>
+      <c r="F3" s="718"/>
+      <c r="G3" s="718"/>
       <c r="M3" s="53"/>
       <c r="N3" s="53"/>
       <c r="O3" s="53"/>
@@ -29439,24 +29438,24 @@
       <c r="I21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="J21" s="723">
+      <c r="J21" s="719">
         <v>225</v>
       </c>
-      <c r="K21" s="724"/>
-      <c r="L21" s="724"/>
-      <c r="M21" s="725"/>
-      <c r="N21" s="723">
+      <c r="K21" s="720"/>
+      <c r="L21" s="720"/>
+      <c r="M21" s="721"/>
+      <c r="N21" s="719">
         <v>475</v>
       </c>
-      <c r="O21" s="724"/>
-      <c r="P21" s="724"/>
-      <c r="Q21" s="725"/>
-      <c r="R21" s="723">
+      <c r="O21" s="720"/>
+      <c r="P21" s="720"/>
+      <c r="Q21" s="721"/>
+      <c r="R21" s="719">
         <v>2475</v>
       </c>
-      <c r="S21" s="724"/>
-      <c r="T21" s="724"/>
-      <c r="U21" s="725"/>
+      <c r="S21" s="720"/>
+      <c r="T21" s="720"/>
+      <c r="U21" s="721"/>
       <c r="W21" s="67" t="s">
         <v>44</v>
       </c>
@@ -29666,7 +29665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -29691,18 +29690,18 @@
       </c>
     </row>
     <row r="3" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="726" t="s">
+      <c r="A3" s="722" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="726"/>
-      <c r="C3" s="726"/>
-      <c r="D3" s="726"/>
-      <c r="E3" s="726"/>
-      <c r="F3" s="726"/>
-      <c r="G3" s="726"/>
-      <c r="H3" s="726"/>
-      <c r="I3" s="726"/>
-      <c r="J3" s="726"/>
+      <c r="B3" s="722"/>
+      <c r="C3" s="722"/>
+      <c r="D3" s="722"/>
+      <c r="E3" s="722"/>
+      <c r="F3" s="722"/>
+      <c r="G3" s="722"/>
+      <c r="H3" s="722"/>
+      <c r="I3" s="722"/>
+      <c r="J3" s="722"/>
       <c r="K3" s="53"/>
       <c r="L3" s="53"/>
       <c r="M3" s="53"/>
@@ -30098,7 +30097,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -31209,7 +31208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet11">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -31244,19 +31243,19 @@
       <c r="F1" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="733" t="s">
+      <c r="T1" s="730" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="733"/>
-      <c r="V1" s="733"/>
-      <c r="W1" s="733"/>
-      <c r="Z1" s="733" t="s">
+      <c r="U1" s="730"/>
+      <c r="V1" s="730"/>
+      <c r="W1" s="730"/>
+      <c r="Z1" s="730" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="733"/>
-      <c r="AB1" s="733"/>
-      <c r="AC1" s="733"/>
-      <c r="AD1" s="733"/>
+      <c r="AA1" s="730"/>
+      <c r="AB1" s="730"/>
+      <c r="AC1" s="730"/>
+      <c r="AD1" s="730"/>
     </row>
     <row r="2" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="81"/>
@@ -31273,15 +31272,15 @@
       <c r="N2" s="82"/>
       <c r="O2" s="82"/>
       <c r="P2" s="83"/>
-      <c r="T2" s="733"/>
-      <c r="U2" s="733"/>
-      <c r="V2" s="733"/>
-      <c r="W2" s="733"/>
-      <c r="Z2" s="733"/>
-      <c r="AA2" s="733"/>
-      <c r="AB2" s="733"/>
-      <c r="AC2" s="733"/>
-      <c r="AD2" s="733"/>
+      <c r="T2" s="730"/>
+      <c r="U2" s="730"/>
+      <c r="V2" s="730"/>
+      <c r="W2" s="730"/>
+      <c r="Z2" s="730"/>
+      <c r="AA2" s="730"/>
+      <c r="AB2" s="730"/>
+      <c r="AC2" s="730"/>
+      <c r="AD2" s="730"/>
     </row>
     <row r="3" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="84"/>
@@ -31300,15 +31299,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="85"/>
-      <c r="T3" s="733"/>
-      <c r="U3" s="733"/>
-      <c r="V3" s="733"/>
-      <c r="W3" s="733"/>
-      <c r="Z3" s="733"/>
-      <c r="AA3" s="733"/>
-      <c r="AB3" s="733"/>
-      <c r="AC3" s="733"/>
-      <c r="AD3" s="733"/>
+      <c r="T3" s="730"/>
+      <c r="U3" s="730"/>
+      <c r="V3" s="730"/>
+      <c r="W3" s="730"/>
+      <c r="Z3" s="730"/>
+      <c r="AA3" s="730"/>
+      <c r="AB3" s="730"/>
+      <c r="AC3" s="730"/>
+      <c r="AD3" s="730"/>
     </row>
     <row r="4" spans="1:35" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="84"/>
@@ -31327,16 +31326,16 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="85"/>
-      <c r="T4" s="733"/>
-      <c r="U4" s="733"/>
-      <c r="V4" s="733"/>
-      <c r="W4" s="733"/>
+      <c r="T4" s="730"/>
+      <c r="U4" s="730"/>
+      <c r="V4" s="730"/>
+      <c r="W4" s="730"/>
       <c r="X4" s="86"/>
-      <c r="Z4" s="733"/>
-      <c r="AA4" s="733"/>
-      <c r="AB4" s="733"/>
-      <c r="AC4" s="733"/>
-      <c r="AD4" s="733"/>
+      <c r="Z4" s="730"/>
+      <c r="AA4" s="730"/>
+      <c r="AB4" s="730"/>
+      <c r="AC4" s="730"/>
+      <c r="AD4" s="730"/>
       <c r="AG4" s="87" t="s">
         <v>29</v>
       </c>
@@ -31359,23 +31358,23 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="85"/>
-      <c r="S5" s="727" t="s">
+      <c r="S5" s="731" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="728"/>
-      <c r="U5" s="728"/>
-      <c r="V5" s="728"/>
-      <c r="W5" s="728"/>
-      <c r="X5" s="728"/>
-      <c r="Y5" s="728"/>
-      <c r="Z5" s="728"/>
-      <c r="AA5" s="728"/>
-      <c r="AB5" s="728"/>
-      <c r="AC5" s="728"/>
-      <c r="AD5" s="728"/>
-      <c r="AE5" s="728"/>
-      <c r="AF5" s="728"/>
-      <c r="AG5" s="729"/>
+      <c r="T5" s="732"/>
+      <c r="U5" s="732"/>
+      <c r="V5" s="732"/>
+      <c r="W5" s="732"/>
+      <c r="X5" s="732"/>
+      <c r="Y5" s="732"/>
+      <c r="Z5" s="732"/>
+      <c r="AA5" s="732"/>
+      <c r="AB5" s="732"/>
+      <c r="AC5" s="732"/>
+      <c r="AD5" s="732"/>
+      <c r="AE5" s="732"/>
+      <c r="AF5" s="732"/>
+      <c r="AG5" s="733"/>
       <c r="AI5" s="86" t="s">
         <v>32</v>
       </c>
@@ -31431,10 +31430,10 @@
       <c r="T6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="U6" s="734" t="s">
+      <c r="U6" s="725" t="s">
         <v>13</v>
       </c>
-      <c r="V6" s="734"/>
+      <c r="V6" s="725"/>
       <c r="W6" s="54" t="s">
         <v>14</v>
       </c>
@@ -31470,20 +31469,20 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="730">
+      <c r="A7" s="729">
         <v>8200</v>
       </c>
-      <c r="B7" s="730">
+      <c r="B7" s="729">
         <v>3</v>
       </c>
       <c r="C7" s="84"/>
-      <c r="D7" s="731">
+      <c r="D7" s="723">
         <v>2211</v>
       </c>
-      <c r="E7" s="731" t="s">
+      <c r="E7" s="723" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="731">
+      <c r="F7" s="723">
         <v>2</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -31573,12 +31572,12 @@
       </c>
     </row>
     <row r="8" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="730"/>
-      <c r="B8" s="730"/>
+      <c r="A8" s="729"/>
+      <c r="B8" s="729"/>
       <c r="C8" s="84"/>
-      <c r="D8" s="731"/>
-      <c r="E8" s="731"/>
-      <c r="F8" s="731"/>
+      <c r="D8" s="723"/>
+      <c r="E8" s="723"/>
+      <c r="F8" s="723"/>
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
@@ -31656,20 +31655,20 @@
       </c>
     </row>
     <row r="9" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="730">
+      <c r="A9" s="729">
         <v>8200</v>
       </c>
-      <c r="B9" s="730">
+      <c r="B9" s="729">
         <v>3</v>
       </c>
       <c r="C9" s="84"/>
-      <c r="D9" s="731">
+      <c r="D9" s="723">
         <v>2213</v>
       </c>
-      <c r="E9" s="731" t="s">
+      <c r="E9" s="723" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="731">
+      <c r="F9" s="723">
         <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -31759,12 +31758,12 @@
       </c>
     </row>
     <row r="10" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="730"/>
-      <c r="B10" s="730"/>
+      <c r="A10" s="729"/>
+      <c r="B10" s="729"/>
       <c r="C10" s="84"/>
-      <c r="D10" s="731"/>
-      <c r="E10" s="731"/>
-      <c r="F10" s="731"/>
+      <c r="D10" s="723"/>
+      <c r="E10" s="723"/>
+      <c r="F10" s="723"/>
       <c r="G10" s="3" t="s">
         <v>10</v>
       </c>
@@ -31842,20 +31841,20 @@
       </c>
     </row>
     <row r="11" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="730">
+      <c r="A11" s="729">
         <v>8200</v>
       </c>
-      <c r="B11" s="730">
+      <c r="B11" s="729">
         <v>3</v>
       </c>
       <c r="C11" s="84"/>
-      <c r="D11" s="731">
+      <c r="D11" s="723">
         <v>2215</v>
       </c>
-      <c r="E11" s="731" t="s">
+      <c r="E11" s="723" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="731">
+      <c r="F11" s="723">
         <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -31945,12 +31944,12 @@
       </c>
     </row>
     <row r="12" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="730"/>
-      <c r="B12" s="730"/>
+      <c r="A12" s="729"/>
+      <c r="B12" s="729"/>
       <c r="C12" s="84"/>
-      <c r="D12" s="732"/>
-      <c r="E12" s="732"/>
-      <c r="F12" s="732"/>
+      <c r="D12" s="724"/>
+      <c r="E12" s="724"/>
+      <c r="F12" s="724"/>
       <c r="G12" s="69" t="s">
         <v>10</v>
       </c>
@@ -32028,20 +32027,20 @@
       </c>
     </row>
     <row r="13" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="730">
+      <c r="A13" s="729">
         <v>8200</v>
       </c>
-      <c r="B13" s="730">
+      <c r="B13" s="729">
         <v>3</v>
       </c>
       <c r="C13" s="84"/>
-      <c r="D13" s="731">
+      <c r="D13" s="723">
         <v>2219</v>
       </c>
-      <c r="E13" s="731" t="s">
+      <c r="E13" s="723" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="731">
+      <c r="F13" s="723">
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -32131,12 +32130,12 @@
       </c>
     </row>
     <row r="14" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="730"/>
-      <c r="B14" s="730"/>
+      <c r="A14" s="729"/>
+      <c r="B14" s="729"/>
       <c r="C14" s="84"/>
-      <c r="D14" s="731"/>
-      <c r="E14" s="731"/>
-      <c r="F14" s="731"/>
+      <c r="D14" s="723"/>
+      <c r="E14" s="723"/>
+      <c r="F14" s="723"/>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
@@ -32214,20 +32213,20 @@
       </c>
     </row>
     <row r="15" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="730">
+      <c r="A15" s="729">
         <v>8200</v>
       </c>
-      <c r="B15" s="730">
+      <c r="B15" s="729">
         <v>3</v>
       </c>
       <c r="C15" s="84"/>
-      <c r="D15" s="731">
+      <c r="D15" s="723">
         <v>2221</v>
       </c>
-      <c r="E15" s="731" t="s">
+      <c r="E15" s="723" t="s">
         <v>2</v>
       </c>
-      <c r="F15" s="731">
+      <c r="F15" s="723">
         <v>4</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -32317,12 +32316,12 @@
       </c>
     </row>
     <row r="16" spans="1:35" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="730"/>
-      <c r="B16" s="730"/>
+      <c r="A16" s="729"/>
+      <c r="B16" s="729"/>
       <c r="C16" s="84"/>
-      <c r="D16" s="731"/>
-      <c r="E16" s="731"/>
-      <c r="F16" s="731"/>
+      <c r="D16" s="723"/>
+      <c r="E16" s="723"/>
+      <c r="F16" s="723"/>
       <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
@@ -32400,20 +32399,20 @@
       </c>
     </row>
     <row r="17" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="730">
+      <c r="A17" s="729">
         <v>8200</v>
       </c>
-      <c r="B17" s="730">
+      <c r="B17" s="729">
         <v>3</v>
       </c>
       <c r="C17" s="84"/>
-      <c r="D17" s="731">
+      <c r="D17" s="723">
         <v>2223</v>
       </c>
-      <c r="E17" s="731" t="s">
+      <c r="E17" s="723" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="731">
+      <c r="F17" s="723">
         <v>7</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -32503,12 +32502,12 @@
       </c>
     </row>
     <row r="18" spans="1:33" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="730"/>
-      <c r="B18" s="730"/>
+      <c r="A18" s="729"/>
+      <c r="B18" s="729"/>
       <c r="C18" s="84"/>
-      <c r="D18" s="732"/>
-      <c r="E18" s="732"/>
-      <c r="F18" s="732"/>
+      <c r="D18" s="724"/>
+      <c r="E18" s="724"/>
+      <c r="F18" s="724"/>
       <c r="G18" s="69" t="s">
         <v>10</v>
       </c>
@@ -32706,23 +32705,23 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="1:33" ht="21" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="S26" s="735" t="s">
+      <c r="S26" s="726" t="s">
         <v>41</v>
       </c>
-      <c r="T26" s="736"/>
-      <c r="U26" s="736"/>
-      <c r="V26" s="736"/>
-      <c r="W26" s="736"/>
-      <c r="X26" s="736"/>
-      <c r="Y26" s="736"/>
-      <c r="Z26" s="736"/>
-      <c r="AA26" s="736"/>
-      <c r="AB26" s="736"/>
-      <c r="AC26" s="736"/>
-      <c r="AD26" s="736"/>
-      <c r="AE26" s="736"/>
-      <c r="AF26" s="736"/>
-      <c r="AG26" s="737"/>
+      <c r="T26" s="727"/>
+      <c r="U26" s="727"/>
+      <c r="V26" s="727"/>
+      <c r="W26" s="727"/>
+      <c r="X26" s="727"/>
+      <c r="Y26" s="727"/>
+      <c r="Z26" s="727"/>
+      <c r="AA26" s="727"/>
+      <c r="AB26" s="727"/>
+      <c r="AC26" s="727"/>
+      <c r="AD26" s="727"/>
+      <c r="AE26" s="727"/>
+      <c r="AF26" s="727"/>
+      <c r="AG26" s="728"/>
     </row>
     <row r="27" spans="1:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H27" s="102"/>
@@ -32759,10 +32758,10 @@
       <c r="T27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="U27" s="734" t="s">
+      <c r="U27" s="725" t="s">
         <v>13</v>
       </c>
-      <c r="V27" s="734"/>
+      <c r="V27" s="725"/>
       <c r="W27" s="54" t="s">
         <v>14</v>
       </c>
@@ -33782,12 +33781,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="S26:AG26"/>
+    <mergeCell ref="S5:AG5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
@@ -33804,27 +33811,19 @@
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="U6:V6"/>
-    <mergeCell ref="S5:AG5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="S26:AG26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet10">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -33870,28 +33869,28 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="738" t="s">
+      <c r="A3" s="734" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="738"/>
-      <c r="C3" s="738"/>
-      <c r="D3" s="738"/>
-      <c r="E3" s="738"/>
-      <c r="F3" s="738"/>
-      <c r="G3" s="738"/>
-      <c r="H3" s="738"/>
-      <c r="I3" s="738"/>
-      <c r="J3" s="738"/>
-      <c r="K3" s="738"/>
-      <c r="L3" s="738"/>
-      <c r="M3" s="738"/>
-      <c r="N3" s="738"/>
-      <c r="O3" s="738"/>
+      <c r="B3" s="734"/>
+      <c r="C3" s="734"/>
+      <c r="D3" s="734"/>
+      <c r="E3" s="734"/>
+      <c r="F3" s="734"/>
+      <c r="G3" s="734"/>
+      <c r="H3" s="734"/>
+      <c r="I3" s="734"/>
+      <c r="J3" s="734"/>
+      <c r="K3" s="734"/>
+      <c r="L3" s="734"/>
+      <c r="M3" s="734"/>
+      <c r="N3" s="734"/>
+      <c r="O3" s="734"/>
       <c r="P3" s="167"/>
       <c r="Q3" s="167"/>
     </row>
     <row r="5" spans="1:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="739" t="s">
+      <c r="A5" s="735" t="s">
         <v>111</v>
       </c>
       <c r="B5" s="33" t="s">
@@ -33926,7 +33925,7 @@
       <c r="Y5" s="190"/>
     </row>
     <row r="6" spans="1:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="740"/>
+      <c r="A6" s="736"/>
       <c r="B6" s="34" t="s">
         <v>390</v>
       </c>
@@ -35193,23 +35192,23 @@
       <c r="Q31" s="167"/>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A32" s="738" t="s">
+      <c r="A32" s="734" t="s">
         <v>603</v>
       </c>
-      <c r="B32" s="738"/>
-      <c r="C32" s="738"/>
-      <c r="D32" s="738"/>
-      <c r="E32" s="738"/>
-      <c r="F32" s="738"/>
-      <c r="G32" s="738"/>
-      <c r="H32" s="738"/>
-      <c r="I32" s="738"/>
-      <c r="J32" s="738"/>
-      <c r="K32" s="738"/>
-      <c r="L32" s="738"/>
-      <c r="M32" s="738"/>
-      <c r="N32" s="738"/>
-      <c r="O32" s="738"/>
+      <c r="B32" s="734"/>
+      <c r="C32" s="734"/>
+      <c r="D32" s="734"/>
+      <c r="E32" s="734"/>
+      <c r="F32" s="734"/>
+      <c r="G32" s="734"/>
+      <c r="H32" s="734"/>
+      <c r="I32" s="734"/>
+      <c r="J32" s="734"/>
+      <c r="K32" s="734"/>
+      <c r="L32" s="734"/>
+      <c r="M32" s="734"/>
+      <c r="N32" s="734"/>
+      <c r="O32" s="734"/>
       <c r="P32" s="44"/>
       <c r="Q32" s="44"/>
     </row>
@@ -35238,28 +35237,28 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="738" t="s">
+      <c r="A35" s="734" t="s">
         <v>635</v>
       </c>
-      <c r="B35" s="738"/>
-      <c r="C35" s="738"/>
-      <c r="D35" s="738"/>
-      <c r="E35" s="738"/>
-      <c r="F35" s="738"/>
-      <c r="G35" s="738"/>
-      <c r="H35" s="738"/>
-      <c r="I35" s="738"/>
-      <c r="J35" s="738"/>
-      <c r="K35" s="738"/>
-      <c r="L35" s="738"/>
-      <c r="M35" s="738"/>
-      <c r="N35" s="738"/>
-      <c r="O35" s="738"/>
+      <c r="B35" s="734"/>
+      <c r="C35" s="734"/>
+      <c r="D35" s="734"/>
+      <c r="E35" s="734"/>
+      <c r="F35" s="734"/>
+      <c r="G35" s="734"/>
+      <c r="H35" s="734"/>
+      <c r="I35" s="734"/>
+      <c r="J35" s="734"/>
+      <c r="K35" s="734"/>
+      <c r="L35" s="734"/>
+      <c r="M35" s="734"/>
+      <c r="N35" s="734"/>
+      <c r="O35" s="734"/>
       <c r="P35" s="167"/>
       <c r="Q35" s="167"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="739" t="s">
+      <c r="A37" s="735" t="s">
         <v>111</v>
       </c>
       <c r="B37" s="50" t="s">
@@ -35276,7 +35275,7 @@
       <c r="I37" s="50"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="740"/>
+      <c r="A38" s="736"/>
       <c r="B38" s="34" t="s">
         <v>390</v>
       </c>
@@ -35560,7 +35559,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -35708,58 +35707,58 @@
       <c r="B5" s="357" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="741" t="s">
+      <c r="C5" s="738" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="743"/>
-      <c r="E5" s="741" t="s">
+      <c r="D5" s="740"/>
+      <c r="E5" s="738" t="s">
         <v>316</v>
       </c>
-      <c r="F5" s="742"/>
-      <c r="G5" s="741" t="s">
+      <c r="F5" s="739"/>
+      <c r="G5" s="738" t="s">
         <v>318</v>
       </c>
-      <c r="H5" s="742"/>
-      <c r="I5" s="741" t="s">
+      <c r="H5" s="739"/>
+      <c r="I5" s="738" t="s">
         <v>320</v>
       </c>
-      <c r="J5" s="742"/>
-      <c r="K5" s="741" t="s">
+      <c r="J5" s="739"/>
+      <c r="K5" s="738" t="s">
         <v>322</v>
       </c>
-      <c r="L5" s="742"/>
-      <c r="M5" s="743" t="s">
+      <c r="L5" s="739"/>
+      <c r="M5" s="740" t="s">
         <v>324</v>
       </c>
-      <c r="N5" s="742"/>
+      <c r="N5" s="739"/>
       <c r="P5" s="356"/>
       <c r="Q5" s="357" t="s">
         <v>135</v>
       </c>
-      <c r="R5" s="741" t="s">
+      <c r="R5" s="738" t="s">
         <v>314</v>
       </c>
-      <c r="S5" s="743"/>
-      <c r="T5" s="741" t="s">
+      <c r="S5" s="740"/>
+      <c r="T5" s="738" t="s">
         <v>316</v>
       </c>
-      <c r="U5" s="742"/>
-      <c r="V5" s="741" t="s">
+      <c r="U5" s="739"/>
+      <c r="V5" s="738" t="s">
         <v>318</v>
       </c>
-      <c r="W5" s="742"/>
-      <c r="X5" s="741" t="s">
+      <c r="W5" s="739"/>
+      <c r="X5" s="738" t="s">
         <v>320</v>
       </c>
-      <c r="Y5" s="742"/>
-      <c r="Z5" s="741" t="s">
+      <c r="Y5" s="739"/>
+      <c r="Z5" s="738" t="s">
         <v>322</v>
       </c>
-      <c r="AA5" s="742"/>
-      <c r="AB5" s="743" t="s">
+      <c r="AA5" s="739"/>
+      <c r="AB5" s="740" t="s">
         <v>324</v>
       </c>
-      <c r="AC5" s="742"/>
+      <c r="AC5" s="739"/>
     </row>
     <row r="6" spans="1:29" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B6" s="358" t="s">
@@ -36296,27 +36295,27 @@
       <c r="B12" s="346" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="746" t="s">
+      <c r="C12" s="737" t="s">
         <v>363</v>
       </c>
-      <c r="D12" s="746"/>
-      <c r="E12" s="746" t="s">
+      <c r="D12" s="737"/>
+      <c r="E12" s="737" t="s">
         <v>362</v>
       </c>
-      <c r="F12" s="746"/>
-      <c r="G12" s="746" t="s">
+      <c r="F12" s="737"/>
+      <c r="G12" s="737" t="s">
         <v>361</v>
       </c>
-      <c r="H12" s="746"/>
-      <c r="I12" s="746" t="s">
+      <c r="H12" s="737"/>
+      <c r="I12" s="737" t="s">
         <v>360</v>
       </c>
-      <c r="J12" s="747"/>
+      <c r="J12" s="741"/>
       <c r="K12" s="345"/>
-      <c r="L12" s="749" t="s">
+      <c r="L12" s="742" t="s">
         <v>389</v>
       </c>
-      <c r="M12" s="746"/>
+      <c r="M12" s="737"/>
       <c r="N12" s="345"/>
       <c r="O12" s="345"/>
       <c r="P12" s="345" t="s">
@@ -36325,26 +36324,26 @@
       <c r="Q12" s="374" t="s">
         <v>135</v>
       </c>
-      <c r="R12" s="744" t="s">
+      <c r="R12" s="743" t="s">
         <v>371</v>
       </c>
-      <c r="S12" s="745"/>
-      <c r="T12" s="746" t="s">
+      <c r="S12" s="744"/>
+      <c r="T12" s="737" t="s">
         <v>372</v>
       </c>
-      <c r="U12" s="746"/>
-      <c r="V12" s="746" t="s">
+      <c r="U12" s="737"/>
+      <c r="V12" s="737" t="s">
         <v>373</v>
       </c>
-      <c r="W12" s="746"/>
-      <c r="X12" s="746" t="s">
+      <c r="W12" s="737"/>
+      <c r="X12" s="737" t="s">
         <v>374</v>
       </c>
-      <c r="Y12" s="747"/>
-      <c r="AA12" s="748" t="s">
+      <c r="Y12" s="741"/>
+      <c r="AA12" s="745" t="s">
         <v>388</v>
       </c>
-      <c r="AB12" s="745"/>
+      <c r="AB12" s="744"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B13" s="367" t="s">
@@ -36762,27 +36761,27 @@
       <c r="B20" s="347" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="746" t="s">
+      <c r="C20" s="737" t="s">
         <v>367</v>
       </c>
-      <c r="D20" s="746"/>
-      <c r="E20" s="746" t="s">
+      <c r="D20" s="737"/>
+      <c r="E20" s="737" t="s">
         <v>366</v>
       </c>
-      <c r="F20" s="746"/>
-      <c r="G20" s="746" t="s">
+      <c r="F20" s="737"/>
+      <c r="G20" s="737" t="s">
         <v>365</v>
       </c>
-      <c r="H20" s="746"/>
-      <c r="I20" s="746" t="s">
+      <c r="H20" s="737"/>
+      <c r="I20" s="737" t="s">
         <v>364</v>
       </c>
-      <c r="J20" s="747"/>
+      <c r="J20" s="741"/>
       <c r="K20" s="373"/>
-      <c r="L20" s="746" t="s">
+      <c r="L20" s="737" t="s">
         <v>386</v>
       </c>
-      <c r="M20" s="746"/>
+      <c r="M20" s="737"/>
       <c r="N20" s="373"/>
       <c r="O20" s="373"/>
       <c r="P20" s="348" t="s">
@@ -36791,26 +36790,26 @@
       <c r="Q20" s="347" t="s">
         <v>135</v>
       </c>
-      <c r="R20" s="746" t="s">
+      <c r="R20" s="737" t="s">
         <v>375</v>
       </c>
-      <c r="S20" s="746"/>
-      <c r="T20" s="746" t="s">
+      <c r="S20" s="737"/>
+      <c r="T20" s="737" t="s">
         <v>376</v>
       </c>
-      <c r="U20" s="746"/>
-      <c r="V20" s="746" t="s">
+      <c r="U20" s="737"/>
+      <c r="V20" s="737" t="s">
         <v>377</v>
       </c>
-      <c r="W20" s="746"/>
-      <c r="X20" s="746" t="s">
+      <c r="W20" s="737"/>
+      <c r="X20" s="737" t="s">
         <v>378</v>
       </c>
-      <c r="Y20" s="747"/>
-      <c r="AA20" s="746" t="s">
+      <c r="Y20" s="741"/>
+      <c r="AA20" s="737" t="s">
         <v>387</v>
       </c>
-      <c r="AB20" s="746"/>
+      <c r="AB20" s="737"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B21" s="367" t="s">
@@ -37223,6 +37222,22 @@
     <row r="27" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
     <mergeCell ref="AA20:AB20"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="K5:L5"/>
@@ -37239,22 +37254,6 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="AA12:AB12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -37262,7 +37261,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -37289,7 +37288,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="752" t="s">
+      <c r="A5" s="748" t="s">
         <v>111</v>
       </c>
       <c r="B5" s="50" t="s">
@@ -37303,7 +37302,7 @@
       <c r="H5" s="50"/>
       <c r="I5" s="50"/>
       <c r="J5" s="13"/>
-      <c r="K5" s="750"/>
+      <c r="K5" s="746"/>
       <c r="L5" s="50" t="s">
         <v>327</v>
       </c>
@@ -37316,7 +37315,7 @@
       <c r="S5" s="443"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="753"/>
+      <c r="A6" s="749"/>
       <c r="B6" s="34" t="s">
         <v>311</v>
       </c>
@@ -37334,7 +37333,7 @@
       </c>
       <c r="I6" s="166"/>
       <c r="J6" s="13"/>
-      <c r="K6" s="751"/>
+      <c r="K6" s="747"/>
       <c r="L6" s="404" t="s">
         <v>299</v>
       </c>
@@ -39545,7 +39544,7 @@
       <c r="A60" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="D60" s="752" t="s">
+      <c r="D60" s="748" t="s">
         <v>111</v>
       </c>
       <c r="E60" s="50" t="s">
@@ -39570,7 +39569,7 @@
       <c r="U60" s="50"/>
     </row>
     <row r="61" spans="1:31" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D61" s="753"/>
+      <c r="D61" s="749"/>
       <c r="E61" s="34" t="s">
         <v>311</v>
       </c>
@@ -40079,7 +40078,7 @@
     </row>
     <row r="69" spans="3:31" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
     <row r="70" spans="3:31" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D70" s="752" t="s">
+      <c r="D70" s="748" t="s">
         <v>111</v>
       </c>
       <c r="E70" s="50" t="s">
@@ -40104,7 +40103,7 @@
       <c r="U70" s="50"/>
     </row>
     <row r="71" spans="3:31" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D71" s="753"/>
+      <c r="D71" s="749"/>
       <c r="E71" s="34" t="s">
         <v>311</v>
       </c>
@@ -40842,7 +40841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet26">
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
@@ -40904,21 +40903,21 @@
       <c r="AG2"/>
     </row>
     <row r="3" spans="1:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="721" t="s">
+      <c r="A3" s="718" t="s">
         <v>636</v>
       </c>
-      <c r="B3" s="721"/>
-      <c r="C3" s="721"/>
-      <c r="D3" s="721"/>
-      <c r="E3" s="721"/>
-      <c r="F3" s="721"/>
-      <c r="G3" s="721"/>
-      <c r="H3" s="721"/>
-      <c r="I3" s="721"/>
-      <c r="J3" s="721"/>
-      <c r="K3" s="721"/>
-      <c r="L3" s="721"/>
-      <c r="M3" s="721"/>
+      <c r="B3" s="718"/>
+      <c r="C3" s="718"/>
+      <c r="D3" s="718"/>
+      <c r="E3" s="718"/>
+      <c r="F3" s="718"/>
+      <c r="G3" s="718"/>
+      <c r="H3" s="718"/>
+      <c r="I3" s="718"/>
+      <c r="J3" s="718"/>
+      <c r="K3" s="718"/>
+      <c r="L3" s="718"/>
+      <c r="M3" s="718"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -40973,22 +40972,22 @@
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
-      <c r="D5" s="718" t="s">
+      <c r="D5" s="750" t="s">
         <v>390</v>
       </c>
-      <c r="E5" s="719"/>
-      <c r="F5" s="719" t="s">
+      <c r="E5" s="751"/>
+      <c r="F5" s="751" t="s">
         <v>391</v>
       </c>
-      <c r="G5" s="719"/>
-      <c r="H5" s="719" t="s">
+      <c r="G5" s="751"/>
+      <c r="H5" s="751" t="s">
         <v>357</v>
       </c>
-      <c r="I5" s="719"/>
-      <c r="J5" s="719" t="s">
+      <c r="I5" s="751"/>
+      <c r="J5" s="751" t="s">
         <v>356</v>
       </c>
-      <c r="K5" s="720"/>
+      <c r="K5" s="752"/>
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
@@ -41576,21 +41575,21 @@
       <c r="AG18"/>
     </row>
     <row r="19" spans="1:33" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="722" t="s">
+      <c r="A19" s="753" t="s">
         <v>202</v>
       </c>
-      <c r="B19" s="722"/>
-      <c r="C19" s="722"/>
-      <c r="D19" s="722"/>
-      <c r="E19" s="722"/>
-      <c r="F19" s="722"/>
-      <c r="G19" s="722"/>
-      <c r="H19" s="722"/>
-      <c r="I19" s="722"/>
-      <c r="J19" s="722"/>
-      <c r="K19" s="722"/>
-      <c r="L19" s="722"/>
-      <c r="M19" s="722"/>
+      <c r="B19" s="753"/>
+      <c r="C19" s="753"/>
+      <c r="D19" s="753"/>
+      <c r="E19" s="753"/>
+      <c r="F19" s="753"/>
+      <c r="G19" s="753"/>
+      <c r="H19" s="753"/>
+      <c r="I19" s="753"/>
+      <c r="J19" s="753"/>
+      <c r="K19" s="753"/>
+      <c r="L19" s="753"/>
+      <c r="M19" s="753"/>
       <c r="N19" s="188"/>
       <c r="O19" s="188"/>
       <c r="P19" s="188"/>
@@ -41607,22 +41606,22 @@
       <c r="AG19"/>
     </row>
     <row r="20" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D20" s="718" t="s">
+      <c r="D20" s="750" t="s">
         <v>390</v>
       </c>
-      <c r="E20" s="719"/>
-      <c r="F20" s="719" t="s">
+      <c r="E20" s="751"/>
+      <c r="F20" s="751" t="s">
         <v>391</v>
       </c>
-      <c r="G20" s="719"/>
-      <c r="H20" s="719" t="s">
+      <c r="G20" s="751"/>
+      <c r="H20" s="751" t="s">
         <v>357</v>
       </c>
-      <c r="I20" s="719"/>
-      <c r="J20" s="719" t="s">
+      <c r="I20" s="751"/>
+      <c r="J20" s="751" t="s">
         <v>356</v>
       </c>
-      <c r="K20" s="720"/>
+      <c r="K20" s="752"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="T20" s="13"/>
@@ -41959,22 +41958,22 @@
       <c r="AG29"/>
     </row>
     <row r="30" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D30" s="718" t="s">
+      <c r="D30" s="750" t="s">
         <v>390</v>
       </c>
-      <c r="E30" s="719"/>
-      <c r="F30" s="719" t="s">
+      <c r="E30" s="751"/>
+      <c r="F30" s="751" t="s">
         <v>391</v>
       </c>
-      <c r="G30" s="719"/>
-      <c r="H30" s="719" t="s">
+      <c r="G30" s="751"/>
+      <c r="H30" s="751" t="s">
         <v>357</v>
       </c>
-      <c r="I30" s="719"/>
-      <c r="J30" s="719" t="s">
+      <c r="I30" s="751"/>
+      <c r="J30" s="751" t="s">
         <v>356</v>
       </c>
-      <c r="K30" s="720"/>
+      <c r="K30" s="752"/>
       <c r="T30" s="13"/>
       <c r="W30"/>
       <c r="X30"/>
